--- a/gom-ai/experiment_results/ket_qua_thuc_nghiem.xlsx
+++ b/gom-ai/experiment_results/ket_qua_thuc_nghiem.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tổng hợp" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dataset 1 (Video thực tế)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dataset 2 (AI tổng hợp)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng hợp" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset 1 (Video thực tế)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset 2 (AI tổng hợp)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G2" s="2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8.15</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="3">
@@ -571,22 +571,22 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>16.77</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>16.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -631,22 +631,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>62.59</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="6"/>
@@ -662,22 +662,22 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="8">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>15.99</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="9">
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>15.75</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="10">
@@ -752,22 +752,22 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>57.21</v>
+        <v>16.7</v>
       </c>
     </row>
   </sheetData>
@@ -781,12 +781,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -794,7 +794,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>9.140000000000001</v>
+        <v>6.62</v>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
     </row>
@@ -922,16 +922,20 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
+          <t>Bát Tràng</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>✗</t>
+        <v>0.8</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -940,13 +944,9 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `llama-3.3-70b-versatile` in o</t>
-        </is>
-      </c>
+        <v>1.59</v>
+      </c>
+      <c r="K3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -969,16 +969,20 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>✗</t>
+        <v>0.85</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -987,13 +991,9 @@
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please </t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>34.47</v>
+        <v>16.68</v>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
     </row>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.15</v>
+        <v>5.01</v>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
     </row>
@@ -1106,16 +1106,20 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+          <t>Biên Hòa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>✗</t>
+        <v>0.9</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1124,13 +1128,9 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `llama-3.3-70b-versatile` in o</t>
-        </is>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1153,16 +1153,20 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>✗</t>
+        <v>0.8</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1171,13 +1175,9 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please </t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1200,27 +1200,1523 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Bình Hòa</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
+          <t>Biên Hòa</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>images/03_phu_lang_vietnam/021_03_phu_lang_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>images/03_phu_lang_vietnam/021_03_phu_lang_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Bát Tràng</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>images/03_phu_lang_vietnam/021_03_phu_lang_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>images/03_phu_lang_vietnam/021_03_phu_lang_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>images/05_chu_dau_vietnam/041_05_chu_dau_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Chu Đậu</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>images/05_chu_dau_vietnam/041_05_chu_dau_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Chu Đậu</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>images/05_chu_dau_vietnam/041_05_chu_dau_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>images/05_chu_dau_vietnam/041_05_chu_dau_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>images/02_bau_truc_vietnam/011_02_bau_truc_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Bàu Trúc</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>images/02_bau_truc_vietnam/011_02_bau_truc_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Bàu Trúc</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>images/02_bau_truc_vietnam/011_02_bau_truc_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>images/02_bau_truc_vietnam/011_02_bau_truc_vietnam_01.jpg</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>images/08_delft_netherlands/071_08_delft_netherlands_01.jpg</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Royal Delft</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>images/08_delft_netherlands/071_08_delft_netherlands_01.jpg</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Royal Delft</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>images/08_delft_netherlands/071_08_delft_netherlands_01.jpg</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>images/08_delft_netherlands/071_08_delft_netherlands_01.jpg</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Royal Delft</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>images/10_meissen_germany/091_10_meissen_germany_01.jpg</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>images/10_meissen_germany/091_10_meissen_germany_01.jpg</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>images/10_meissen_germany/091_10_meissen_germany_01.jpg</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>images/10_meissen_germany/091_10_meissen_germany_01.jpg</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>images/07_kakiemon_japan/061_07_kakiemon_japan_01.jpg</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Arita</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>images/07_kakiemon_japan/061_07_kakiemon_japan_01.jpg</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Arita-yaki</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>images/07_kakiemon_japan/061_07_kakiemon_japan_01.jpg</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>images/07_kakiemon_japan/061_07_kakiemon_japan_01.jpg</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Arita</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>images/09_iznik_turkey/081_09_iznik_turkey_01.jpg</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>images/09_iznik_turkey/081_09_iznik_turkey_01.jpg</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>images/09_iznik_turkey/081_09_iznik_turkey_01.jpg</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>images/09_iznik_turkey/081_09_iznik_turkey_01.jpg</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>images/06_goryeo_south_korea/051_06_goryeo_south_korea_01.jpg</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Gốm Hoa Của</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>90.70999999999999</v>
-      </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>images/06_goryeo_south_korea/051_06_goryeo_south_korea_01.jpg</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Yaozhou</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>images/06_goryeo_south_korea/051_06_goryeo_south_korea_01.jpg</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>images/06_goryeo_south_korea/051_06_goryeo_south_korea_01.jpg</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Gốm Hoa Của</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1233,14 +2729,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -1327,10 +2823,14 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Deruta</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr"/>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="n">
         <v>0.85</v>
       </c>
@@ -1341,11 +2841,11 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>4.98</v>
+        <v>5.19</v>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
     </row>
@@ -1370,12 +2870,16 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
@@ -1388,13 +2892,9 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `llama-3.3-70b-versatile` in o</t>
-        </is>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="K3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1417,12 +2917,16 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
@@ -1435,13 +2939,9 @@
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please </t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1464,10 +2964,14 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Deruta</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
         <v>0.85</v>
       </c>
@@ -1478,11 +2982,11 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>38.56</v>
+        <v>16.33</v>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
     </row>
@@ -1529,7 +3033,7 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.48</v>
+        <v>7.76</v>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
     </row>
@@ -1554,16 +3058,20 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>✗</t>
+        <v>0.8</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1572,13 +3080,9 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `llama-3.3-70b-versatile` in o</t>
-        </is>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1601,16 +3105,20 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>✗</t>
+        <v>0.8</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1619,13 +3127,9 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please </t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1670,9 +3174,1509 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>75.86</v>
+        <v>18.34</v>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>images/03_phu_lang/021_03_phu_lang_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>images/03_phu_lang/021_03_phu_lang_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>images/03_phu_lang/021_03_phu_lang_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>images/03_phu_lang/021_03_phu_lang_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>images/04_chu_dau/031_04_chu_dau_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>images/04_chu_dau/031_04_chu_dau_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>images/04_chu_dau/031_04_chu_dau_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>images/04_chu_dau/031_04_chu_dau_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>images/05_bau_truc/041_05_bau_truc_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>images/05_bau_truc/041_05_bau_truc_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>images/05_bau_truc/041_05_bau_truc_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>images/05_bau_truc/041_05_bau_truc_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>images/08_delft/071_08_delft_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>images/08_delft/071_08_delft_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>images/08_delft/071_08_delft_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>images/08_delft/071_08_delft_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Delftware</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>images/10_meissen/091_10_meissen_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>images/10_meissen/091_10_meissen_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>images/10_meissen/091_10_meissen_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>images/10_meissen/091_10_meissen_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Meissen</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>images/07_arita/061_07_arita_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Arita</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>images/07_arita/061_07_arita_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Kakiemon</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>images/07_arita/061_07_arita_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>images/07_arita/061_07_arita_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>images/09_iznik/081_09_iznik_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>images/09_iznik/081_09_iznik_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>images/09_iznik/081_09_iznik_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>images/09_iznik/081_09_iznik_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>images/06_goryeo/051_06_goryeo_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>CHATGPT</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>images/06_goryeo/051_06_goryeo_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>GROK</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Gwangju Celadon</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>images/06_goryeo/051_06_goryeo_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>GEMINI</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>images/06_goryeo/051_06_goryeo_01_vase.jpg</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ACIS</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gom-ai/experiment_results/ket_qua_thuc_nghiem.xlsx
+++ b/gom-ai/experiment_results/ket_qua_thuc_nghiem.xlsx
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,12 +61,6 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-        <bgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -86,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -104,9 +98,6 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -737,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3.43</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -2736,13 +2727,13 @@
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4233,12 +4224,16 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
+          <t>Famille Rose Porcelain (Jingdezhen production)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -4251,13 +4246,9 @@
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please </t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
